--- a/data/seguidores tiktok.xlsx
+++ b/data/seguidores tiktok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E65F817-15D8-46AF-81FC-940CE76A9F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F15E8A-F2B0-49D6-82BA-C338E6250915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -365,7 +365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -393,6 +393,17 @@
         <v>162700</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B3" s="3">
+        <v>7111</v>
+      </c>
+      <c r="C3" s="3">
+        <v>162700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/seguidores tiktok.xlsx
+++ b/data/seguidores tiktok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F15E8A-F2B0-49D6-82BA-C338E6250915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DDEA61-AC26-40F6-B48F-7B3B5BA9B6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,7 +365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -404,6 +404,17 @@
         <v>162700</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B4">
+        <v>7123</v>
+      </c>
+      <c r="C4" s="3">
+        <v>162700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/seguidores tiktok.xlsx
+++ b/data/seguidores tiktok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DDEA61-AC26-40F6-B48F-7B3B5BA9B6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D8A316-19CD-4E2D-A2CB-05393FAD1293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -365,13 +365,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,7 +382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>46310</v>
       </c>
@@ -393,7 +393,7 @@
         <v>162700</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46311</v>
       </c>
@@ -404,15 +404,26 @@
         <v>162700</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>46312</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>7123</v>
       </c>
       <c r="C4" s="3">
         <v>162700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B5" s="3">
+        <v>7144</v>
+      </c>
+      <c r="C5" s="3">
+        <v>162600</v>
       </c>
     </row>
   </sheetData>

--- a/data/seguidores tiktok.xlsx
+++ b/data/seguidores tiktok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D8A316-19CD-4E2D-A2CB-05393FAD1293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8DD541-4DC6-4122-8C40-92FA0E8226AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,7 +365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -426,6 +426,17 @@
         <v>162600</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B6" s="3">
+        <v>7169</v>
+      </c>
+      <c r="C6" s="3">
+        <v>162600</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/seguidores tiktok.xlsx
+++ b/data/seguidores tiktok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Documents\Seguidores RN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8DD541-4DC6-4122-8C40-92FA0E8226AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC1D297-3096-4A19-AEB9-513D42877000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -365,13 +365,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,7 +382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46310</v>
       </c>
@@ -393,7 +393,7 @@
         <v>162700</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46311</v>
       </c>
@@ -404,7 +404,7 @@
         <v>162700</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46312</v>
       </c>
@@ -415,7 +415,7 @@
         <v>162700</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46313</v>
       </c>
@@ -426,7 +426,7 @@
         <v>162600</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46314</v>
       </c>
@@ -434,6 +434,17 @@
         <v>7169</v>
       </c>
       <c r="C6" s="3">
+        <v>162600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B7" s="3">
+        <v>7183</v>
+      </c>
+      <c r="C7" s="3">
         <v>162600</v>
       </c>
     </row>
